--- a/docs/PPG/Financiadores.xlsx
+++ b/docs/PPG/Financiadores.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10510"/>
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0DF11D-D278-8E4C-BA59-9D3C1D24F230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A97A6BBD-E37F-514A-95B9-F9FC875F3AF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="940" yWindow="680" windowWidth="27880" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="396">
   <si>
     <t>CAPEX</t>
   </si>
@@ -1218,6 +1218,12 @@
   </si>
   <si>
     <t>E-26/200.037/2026</t>
+  </si>
+  <si>
+    <t>Edital nº 23/2025</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2025/chamada-no-23-2025/ResultadoPreliminarChamada232025.pdf</t>
   </si>
 </sst>
 </file>
@@ -1467,7 +1473,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1551,9 +1557,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1972,7 +1975,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M196"/>
+  <dimension ref="A1:M200"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="9"/>
@@ -8146,7 +8149,7 @@
       <c r="D190" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="E190" s="29" t="s">
+      <c r="E190" s="7" t="s">
         <v>393</v>
       </c>
       <c r="F190" s="7" t="s">
@@ -8321,6 +8324,103 @@
       <c r="J196" s="8">
         <f>4100*36/3</f>
         <v>49200</v>
+      </c>
+    </row>
+    <row r="197" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+      <c r="A197" s="9">
+        <v>121</v>
+      </c>
+      <c r="B197" s="6">
+        <v>2025</v>
+      </c>
+      <c r="C197" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D197" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="E197" s="22" t="s">
+        <v>364</v>
+      </c>
+      <c r="F197" s="22" t="s">
+        <v>364</v>
+      </c>
+      <c r="G197" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H197" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="I197" s="27">
+        <f>SUM(J198:J200)</f>
+        <v>75600</v>
+      </c>
+      <c r="J197" s="14"/>
+      <c r="K197" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="L197" s="21" t="s">
+        <v>395</v>
+      </c>
+      <c r="M197" s="5" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="198" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="A198" s="9">
+        <v>121</v>
+      </c>
+      <c r="B198" s="6">
+        <v>2026</v>
+      </c>
+      <c r="C198" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H198" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="I198" s="14"/>
+      <c r="J198" s="14">
+        <f>12*(1100+1000)</f>
+        <v>25200</v>
+      </c>
+    </row>
+    <row r="199" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="A199" s="9">
+        <v>121</v>
+      </c>
+      <c r="B199" s="6">
+        <v>2027</v>
+      </c>
+      <c r="C199" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H199" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="I199" s="14"/>
+      <c r="J199" s="14">
+        <f>12*(1100+1000)</f>
+        <v>25200</v>
+      </c>
+    </row>
+    <row r="200" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="A200" s="9">
+        <v>121</v>
+      </c>
+      <c r="B200" s="6">
+        <v>2028</v>
+      </c>
+      <c r="C200" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H200" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="I200" s="14"/>
+      <c r="J200" s="14">
+        <f>12*(1100+1000)</f>
+        <v>25200</v>
       </c>
     </row>
   </sheetData>
